--- a/AAII_Financials/Quarterly/VIV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VIV_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
   <si>
     <t>VIV</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3041500</v>
+      </c>
+      <c r="E8" s="3">
         <v>2963200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2834200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2805000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2687800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2510000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2357600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2578200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2464000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2700800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2789300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2625500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2640700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2512300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2275200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2253900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2371200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2334200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2321300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2222100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2062100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2029700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2190400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2102000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2033100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1932400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2101300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2072100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1924700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2053700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1977700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1991800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2527500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2519400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2828800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2790900</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2742500</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2627200</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2697500</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>2652800</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1656400</v>
+      </c>
+      <c r="E9" s="3">
         <v>892300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1489900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1432300</v>
       </c>
-      <c r="G9" s="3">
-        <v>1389300</v>
-      </c>
       <c r="H9" s="3">
+        <v>1473100</v>
+      </c>
+      <c r="I9" s="3">
         <v>734100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1282200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1337400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1280400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1396100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1482100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1382200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1360500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1323300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1303700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1302600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1336300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1328400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1349700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1246600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1162700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1103900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1162700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1141100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1068500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>976700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1072600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1029600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>960300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1018000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>998800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>944100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1238500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1172500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1307500</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1306400</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1286600</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1254900</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1213900</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>1308100</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1385100</v>
+      </c>
+      <c r="E10" s="3">
         <v>2070800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1344300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1372700</v>
       </c>
-      <c r="G10" s="3">
-        <v>1298400</v>
-      </c>
       <c r="H10" s="3">
+        <v>1214700</v>
+      </c>
+      <c r="I10" s="3">
         <v>1775900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1075400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1240900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1183600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1304600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1307200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1243200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1280200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1189000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>971500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>951300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1034900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1005800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>971700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>975500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>899400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>925800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1027700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>960900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>964600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>955700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1028700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1042500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>964500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1035700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>978800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1047700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1289000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1347000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1521200</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1484500</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1455900</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1372300</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>1483600</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>1344700</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,115 +1496,118 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>55400</v>
+      </c>
+      <c r="E14" s="3">
         <v>400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>60200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>72700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>68500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-52200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>46100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>29000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>33900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-123100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>69200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>47400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>19300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-38700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-18000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-39300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-26200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-103600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-34700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-316400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-40300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-53500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-51500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-73600</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-14700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-19700</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-23900</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-22900</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-26300</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>-38200</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>-280000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>-501200</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>-20700</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>-21800</v>
-      </c>
-      <c r="AL14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AM14" s="3" t="s">
         <v>8</v>
@@ -1601,130 +1621,136 @@
       <c r="AP14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>436600</v>
+      </c>
+      <c r="E15" s="3">
         <v>744500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>398600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>405800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>400200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>647900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>358600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>406900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>358500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>395600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>409100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>420400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>382300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>381100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>106800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>108100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>117600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>120200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>117500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>117200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>114200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>111400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>117700</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>114900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>116200</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>103700</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>107100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>112900</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>102100</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>100600</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>86900</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>87900</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>108300</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>106300</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>114300</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>121600</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>121200</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>117400</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>115000</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>119200</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2505000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2517300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2282700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2252600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2236900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2163300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1988100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2131600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2067300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2285900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2318200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2167200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2203800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2160800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1922800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1934900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2075100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2039500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1946000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1839900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1718000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1739400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1808100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1802300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1771700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1617700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1735700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1727800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1636500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1722100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1670300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1484800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1782400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2099900</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2373400</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2351300</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2339600</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2237400</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>2248900</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>2296100</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>536500</v>
+      </c>
+      <c r="E18" s="3">
         <v>445900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>551500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>552400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>450900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>346700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>369500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>446700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>396600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>414800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>471100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>458200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>436900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>351500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>352400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>319000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>296100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>294800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>375400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>382200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>344100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>290300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>382400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>299700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>261400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>314700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>365600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>344300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>288200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>331600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>307300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>507100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>745100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>419600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>455300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>439700</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>403000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>389800</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>448600</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>356700</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,618 +2085,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-20400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>48500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>162000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-24900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>5600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>34100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-20300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>81900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-41500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-8100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-20600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>5000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>11000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-23600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>16900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>16600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-9800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-11300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-5000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>19700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>142300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>368700</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-3600</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-5300</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>18000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-6100</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>900</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-23600</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>967800</v>
+      </c>
+      <c r="E21" s="3">
         <v>1190200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>950400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>955300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>854300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>994900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>729700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>852700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>775500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>761900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>718100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>903500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>813600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>698600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>918600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>996800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>875300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>918800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>973700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1002200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>938500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>810200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>946300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>858700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>825400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>794800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>916500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>840400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>750300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>835600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>722600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1025800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1583800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>882600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>960500</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>960700</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>898700</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>872800</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>875400</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>845200</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>164300</v>
+      </c>
+      <c r="E22" s="3">
         <v>138000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>143300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>139400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>154000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>99200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>123100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>117900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>121800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>127500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>137700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>140500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>128200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>131100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>88200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>88800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>79000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>99700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>60200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>56300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>41400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>35200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>48300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>20100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>31400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>24900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>32700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>46100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>37700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>36500</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>23200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>21300</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>25200</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>36700</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>40300</v>
-      </c>
-      <c r="AL22" s="3">
-        <v>61700</v>
       </c>
       <c r="AM22" s="3">
         <v>61700</v>
       </c>
       <c r="AN22" s="3">
+        <v>61700</v>
+      </c>
+      <c r="AO22" s="3">
         <v>72900</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>54700</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>72700</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>363600</v>
+      </c>
+      <c r="E23" s="3">
         <v>307300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>399000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>394500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>285500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>247000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>337600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>323600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>304400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>244000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>334000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>310000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>287600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>201100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>243900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>312100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>175600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>187000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>294600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>331000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>313600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>231400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>326100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>296500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>246700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>279900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>331700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>286900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>245600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>314800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>285000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>628000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1088600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>379200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>409700</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>396000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>335200</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>317700</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>370400</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>283200</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>61000</v>
+      </c>
+      <c r="E24" s="3">
         <v>66500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>54900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>40400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>39800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>62800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>52800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>17300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>82500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>65300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>14300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>55100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>36300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>41500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>46700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>26200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>32800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-235800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>66200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>53200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>55200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>73100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>60500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>27400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>74000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>96300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>105900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-5800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>63700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>19800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>40100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>349200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>122800</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>20800</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>82500</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>111400</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>70600</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>69000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>46900</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>302600</v>
+      </c>
+      <c r="E26" s="3">
         <v>240800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>344100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>354100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>245700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>184200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>284800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>306300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>221800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>178700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>331300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>295700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>232500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>164800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>202400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>265400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>149400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>154200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>530400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>264800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>260400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>176300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>253000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>236000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>219300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>205900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>235400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>181000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>251400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>251200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>265200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>587900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>739400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>256400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>388900</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>313500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>223800</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>247100</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>301400</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>236300</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>303500</v>
+      </c>
+      <c r="E27" s="3">
         <v>241700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>340800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>354300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>246700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>184500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>285100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>306200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>220100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>178600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>329900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>294700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>232800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>164800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>202400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>266000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>152900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>155500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>531800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>265400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>260400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>176300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>253000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>236000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>219300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>205900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>235400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>181000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>251400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>251200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>265200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>587900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>739400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>256400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>388900</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>313500</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>223800</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>247100</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>301400</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>236300</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>20400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-48500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-162000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>24900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-5600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-34100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>20300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-81900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>41500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>8100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>20600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-5000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-11000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>23600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>8000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-16900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-16600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>9800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>11300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>5000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-19700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-142300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-368700</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>3600</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>5300</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-18000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>6100</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-900</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>23600</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>303500</v>
+      </c>
+      <c r="E33" s="3">
         <v>241700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>340800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>354300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>246700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>184500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>285100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>306200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>220100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>178600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>329900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>294700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>232800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>164800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>202400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>266000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>152900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>155500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>531800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>265400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>260400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>176300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>253000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>236000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>219300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>205900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>235400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>181000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>251400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>251200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>265200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>587900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>739400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>256400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>388900</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>313500</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>223800</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>247100</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>301400</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>236300</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>303500</v>
+      </c>
+      <c r="E35" s="3">
         <v>241700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>340800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>354300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>246700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>184500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>285100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>306200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>220100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>178600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>329900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>294700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>232800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>164800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>202400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>266000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>152900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>155500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>531800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>265400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>260400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>176300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>253000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>236000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>219300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>205900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>235400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>181000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>251400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>251200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>265200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>587900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>739400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>256400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>388900</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>313500</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>223800</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>247100</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>301400</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>236300</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,142 +4305,146 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1637700</v>
+      </c>
+      <c r="E41" s="3">
         <v>1737300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1276800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1275300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1735100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1427600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1081800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1248600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1324800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1347000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>898200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>912200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1120900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1022800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>408700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1113400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>627600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1322300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1301600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1749800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1628900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1290500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1127600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1627600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1610800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>978200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>626800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>853200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1037300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>762500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>603200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>687200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1034400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1016900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1038400</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1428300</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1909300</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1559200</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1266500</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>1437500</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>17700</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>18000</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
@@ -4374,7 +4464,7 @@
         <v>0</v>
       </c>
       <c r="M42" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="N42" s="3">
         <v>200</v>
@@ -4395,19 +4485,19 @@
         <v>200</v>
       </c>
       <c r="T42" s="3">
+        <v>200</v>
+      </c>
+      <c r="U42" s="3">
         <v>6300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>6100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>8000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>4300</v>
-      </c>
-      <c r="X42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y42" s="3" t="s">
         <v>8</v>
@@ -4424,8 +4514,8 @@
       <c r="AC42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD42" s="3">
-        <v>0</v>
+      <c r="AD42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE42" s="3">
         <v>0</v>
@@ -4463,862 +4553,886 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2600700</v>
+      </c>
+      <c r="E43" s="3">
         <v>1974800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2480700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2451800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2245300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2201700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2042100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2256800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2223400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2448100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2474800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2332100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2342100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2316200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2181500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2239100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2323900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2463900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2523100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2553600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2491000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2119800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2208800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2319600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2300600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2286200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2469800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2665400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2541400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2591700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2384800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2283300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2595700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2694600</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2901400</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>2974400</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>3036200</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>2869600</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>2971200</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>2753100</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>344400</v>
+      </c>
+      <c r="E44" s="3">
         <v>336600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>268000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>235700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>182000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>211000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>177400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>220600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>185700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>206700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>169600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>177900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>157800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>223500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>141900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>142400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>160500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>163800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>129100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>119900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>130800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>189400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>123900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>101400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>122100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>129300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>106800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>125700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>102600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>101900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>82400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>85000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>114700</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>119200</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>89400</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>97600</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>100000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>98600</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>101800</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>124100</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>132700</v>
+      </c>
+      <c r="E45" s="3">
         <v>1440000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>97100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>96700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>114600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>85500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>85200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>100700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>92600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>143300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>127800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>125700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>75500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>82900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>374100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>402300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>455500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>499700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>291000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>343900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>442000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>497300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>269900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>291300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>367600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>381000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>240400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>242500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>348900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>326300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>205500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>247300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>379000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>351700</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>260400</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>286100</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>402900</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>438400</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>224900</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>258600</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5392400</v>
+      </c>
+      <c r="E46" s="3">
         <v>5488700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4578800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4550000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4833600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4499400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3688700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4238000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4294200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4684800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3966200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3884800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4127900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4118300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3106400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3897400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3567800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4456100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4250800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4775200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4697100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4097000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3730200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4339900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4401100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3774600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3443700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3886800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4030200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3782400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3276000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>3302800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>4123900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>4182400</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>4289700</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>4786400</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>5448300</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>4965900</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>4564400</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>4573200</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D47" s="3">
+        <v>79700</v>
+      </c>
+      <c r="E47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>76400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>118800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>109200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>102900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>91600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>96800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>88900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>90000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>90400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>86900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>90000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>84500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>334500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>381700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>515000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>526800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>519300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>448400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>312000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>249600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>273100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>280300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>376200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>258000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>267800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>263100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>311600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>490100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>670000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1032300</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1189400</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>275000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>286800</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>209000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>211900</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>215200</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>216000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>269200</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8867200</v>
+      </c>
+      <c r="E48" s="3">
         <v>8890600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8597900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8392800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8300300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7980500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7568800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8415900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8199200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9100000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>9545600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9106400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9222300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8902900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8249300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8413800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>9138900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>9212700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>8963400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>8876200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>8583300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>8289700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>8679800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>8127800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>8230900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>7506200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>7913900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>8077000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>7592800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>7898400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>6086200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>6316100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>7816600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>7732800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>8517500</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>8311100</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>8155700</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>7857500</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>7919900</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>7621600</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9136100</v>
+      </c>
+      <c r="E49" s="3">
         <v>9128500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8708900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8917100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8761000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8366800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7803100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8846600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8710600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9696100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10090700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9825000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10174400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>9751000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>8937100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>9143800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>9991700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>9014200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>8902000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>8018800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>7777200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>7553100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>7941900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>7883700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>8039200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>7336400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>7623500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>7792500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>7383200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>7838900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>7532200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>7848000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>9976700</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>10037600</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>11109400</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>11126200</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>11225000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>10935700</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>11035500</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>11102400</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1270500</v>
+      </c>
+      <c r="E52" s="3">
         <v>1430000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1181400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1217600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1140600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1050500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>963200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1023300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>969000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1029300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1080900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1031400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1206400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1108200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>782300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>772800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>839000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>744100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>710000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>690400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>653600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>624600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>655100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>645500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>765600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>728800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>752200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>742600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>702000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>769200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>732500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>805900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1329100</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1656900</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1789100</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1791700</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1714000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1666100</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>1584700</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>1665400</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>24883200</v>
+      </c>
+      <c r="E54" s="3">
         <v>25012800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>23251900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>23248300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>23211700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>22081600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>20200900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>22711300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>22351900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>24695300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>24882600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>24026600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>24920100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>24062900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>21409700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>22609500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>24052400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>23953800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>23345500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>22809100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>22023200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>20814000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>21280100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>21277300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>21813000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>19604100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>20001100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>20762100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>20019700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>20778900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>18296900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>19305000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>24435800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>23884700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>25992500</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>26224400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>26754900</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>25640400</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>25320600</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>25231800</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,740 +6145,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1934800</v>
+      </c>
+      <c r="E57" s="3">
         <v>1961400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1790400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1788500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1728800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1658700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1492400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1789200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1778200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1884300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1683700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1802900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1823400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1876700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1332800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1432100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1701500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1652400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1439600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1499600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1414700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1454900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1294200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1338100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1129500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1130100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1269200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1330300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1285600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1330300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1363500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1500500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1873100</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1702000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1909300</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1869200</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1822100</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1699100</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>1888200</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>1833200</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1021800</v>
+      </c>
+      <c r="E58" s="3">
         <v>995500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>980700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>925700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1249800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1152400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1042700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1114600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>825100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>880100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>923800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>877400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1218100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1114700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1082000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1108600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>923100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1015800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1394100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>888200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>851800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>755500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>720700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>935000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>957500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>877000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>762200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>503400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>557700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>560000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>261200</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>279400</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>359000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>658300</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>777700</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>873800</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>1420400</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>1105200</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>1156900</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>921800</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2142600</v>
+      </c>
+      <c r="E59" s="3">
         <v>1826000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1287800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1223600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1430500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1411000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>925300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>966200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1056400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1357400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>946000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>947100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1145600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1225200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1569900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2039000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2503800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1798000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1699500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2093400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2266000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1631400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1483300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1642300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2212500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1414800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1243700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1733400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2095500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1469000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1436800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1867600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2333300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1776200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1892600</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>2249700</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>2450000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1875100</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>2025300</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>2310100</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5671500</v>
+      </c>
+      <c r="E60" s="3">
         <v>4994500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4583500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4480700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4919300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4666900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3922100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4408100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4173600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4637100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4139100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4213700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4733900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4649600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3984700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4579700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5128300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4466200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>4533200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4481200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4532600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3841800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3498200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3915500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4299500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3421900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3275100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3567100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3938800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>3359300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>3061500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>3647500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>4565400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>4136500</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>4579600</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>4992600</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>5692600</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>4679400</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>5070400</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>5065100</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2809400</v>
+      </c>
+      <c r="E61" s="3">
         <v>2813600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2730900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2472700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2483700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2434600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2313500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2425500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2579200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2816800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2957200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2695600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2593300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2674600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2387100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2539900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2360300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2189400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2023900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1671100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1654600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1647900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1870200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1525600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1633600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1512100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1791300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2068400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2051900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2096100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>834100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>887300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1160300</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1216700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1391700</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1191800</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>1251600</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>1579700</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>1131400</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>1272300</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2732600</v>
+      </c>
+      <c r="E62" s="3">
         <v>3018900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2463600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2498200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2384400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2233600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1897200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2280600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2252800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2829100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2490900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2381700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2403700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2259100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2734200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2714600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2918000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2867900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2658400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2680500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2520100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2224600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2299400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2231300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2235100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1957000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1921600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1881100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1693300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1803800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1626700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1547600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>2111100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>2086400</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>2212700</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>2218400</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>2208400</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>2069800</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>1940600</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>1860400</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>12201100</v>
+      </c>
+      <c r="E66" s="3">
         <v>11637200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>10724200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>10395000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>10706300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10196300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>8915500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10021100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9894700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10992600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10533300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10145000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>10671600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>10471400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9115500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>9844000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>10417800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>9538600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>9231400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>8841900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>8707300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>7714200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>7667800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>7672400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>8168100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>6891100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>6988000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>7516600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>7684000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>7259200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>5522200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>6082500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>7836800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>7439500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>8184000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>8402800</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>9152500</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>8329000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>8142400</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>8197700</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="D72" s="3">
+        <v>2106200</v>
+      </c>
+      <c r="E72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1585900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1677500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1445600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1465300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1216400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1254300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1287600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1292200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1212900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1159400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1032200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1001200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>968300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1096100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>946000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1360500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1391500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1249600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1045500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>928800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>869400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1224900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1121600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>978100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>876500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1331400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1088800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1172900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1003600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1469900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1767000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>1103100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>965200</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>1541100</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>1320900</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>1083900</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>951500</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>1282900</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12667800</v>
+      </c>
+      <c r="E76" s="3">
         <v>13375600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12476700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12841600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12493900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11873400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11274200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>12677000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>12444400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13690500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14336900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13870400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>14238000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>13581200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12294200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>12765600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>13634600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>14415300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>14114100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>13967200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>13315900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>13099800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>13612300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>13604900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>13644900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>12713000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>13013100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>13245400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>12335800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>13519700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>12774700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>13222500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>16599000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>16445200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>17808500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>17821500</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>17602400</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>17311400</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>17178200</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>17034100</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>303500</v>
+      </c>
+      <c r="E81" s="3">
         <v>241700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>340800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>354300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>246700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>184500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>285100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>306200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>220100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>178600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>329900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>294700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>232800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>164800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>202400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>266000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>152900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>155500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>531800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>265400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>260400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>176300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>253000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>236000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>219300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>205900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>235400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>181000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>251400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>251200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>265200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>587900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>739400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>256400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>388900</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>313500</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>223800</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>247100</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>301400</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>236300</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>498600</v>
+      </c>
+      <c r="E83" s="3">
         <v>477100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>445200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>495000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>443000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>484800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>520500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>467500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>485400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>462200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>445700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>428500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>420800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>476200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>586500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>596000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>620700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>632100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>618900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>614900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>583500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>543600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>571900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>542100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>547300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>490000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>552100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>507400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>467000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>484400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>414400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>376500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>470000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>466600</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>510400</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>503000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>501800</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>482200</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>450300</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>489300</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E89" s="3">
+      <c r="E89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F89" s="3">
         <v>934100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>864800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1077800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>887900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>738900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>855900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1030500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>982000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>790300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>949000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1128600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>942100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>840300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>944900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>940500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>917000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>824600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1073600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>789700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>856500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>837000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1029000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1029400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>813700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>906900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>898200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>797900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>658100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>819000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>451400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>458900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>687900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>759700</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>995800</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1056700</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>414900</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>823100</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>764700</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E91" s="3">
+      <c r="E91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" s="3">
         <v>-442400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-442100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-411700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-422300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-437200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-440500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-399300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-399700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-548900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-468500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-515600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-261100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2963800</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-2195800</v>
       </c>
       <c r="S91" s="3">
         <v>-2195800</v>
       </c>
       <c r="T91" s="3">
+        <v>-2195800</v>
+      </c>
+      <c r="U91" s="3">
         <v>-1815300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2739600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2423500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-418900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-368300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-490100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-296200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-421000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-379800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-416800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-435000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-381700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-394400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-468000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-401000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-380100</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-490200</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-721700</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-525300</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-437900</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-445500</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-482400</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-465500</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E94" s="3">
+      <c r="E94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F94" s="3">
         <v>-603200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-405700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-394400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-415700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-433900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-398400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-387700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-380700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-464700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-414900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-486600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-232600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-575500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-486100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1362300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-323400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-489800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-379800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-383700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-343100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-400100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-187000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-375100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-267900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-362000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-346100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-359900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-391000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-444400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-150600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-62600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-491100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-705700</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-552100</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-411400</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-478200</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-489300</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-476000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,130 +10455,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E96" s="3">
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3">
         <v>57700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>343000</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>114900</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>328000</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>67800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>356400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>357200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-617900</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-419600</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-548100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-440200</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
         <v>0</v>
       </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-418600</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-607700</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
         <v>0</v>
       </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-650800</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-497600</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-100</v>
       </c>
       <c r="AF96" s="3">
         <v>-100</v>
       </c>
       <c r="AG96" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-380600</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-370500</v>
-      </c>
-      <c r="AI96" s="3">
-        <v>-100</v>
       </c>
       <c r="AJ96" s="3">
         <v>-100</v>
       </c>
       <c r="AK96" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-606200</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-334200</v>
-      </c>
-      <c r="AM96" s="3">
-        <v>-100</v>
       </c>
       <c r="AN96" s="3">
         <v>-100</v>
       </c>
       <c r="AO96" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AP96" s="3">
         <v>-470300</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-265400</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,130 +10953,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E100" s="3">
+      <c r="E100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F100" s="3">
         <v>-288000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-957800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-450500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-211600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-322300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-559700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-534900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-123300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-366200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-704100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-595100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-135800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-939300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>76000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-239300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-597300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-786800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-638400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-112800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-300900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-944600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-806500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-123300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-173400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-758200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-797800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-122300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-137300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-433900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-433300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-378600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-125800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-611900</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-924700</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-179400</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>356100</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-504800</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-259100</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10876,8 +11125,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10954,8 +11203,11 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -10963,117 +11215,120 @@
         <v>0</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>42800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-498700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>232900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>260600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-17400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-102200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>107900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>478000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-40600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-170100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>46900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>573700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-674400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>534800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-661200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-3700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-452000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>55500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>293300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>212500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-507700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>35500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>531000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>372400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-213300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-245700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>315700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>129800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-59300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-132500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>17600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>71000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-389900</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-481000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>297900</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>292700</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-171000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>29500</v>
       </c>
     </row>
